--- a/docs/FX_Feedback_Assessment.xlsx
+++ b/docs/FX_Feedback_Assessment.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,14 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +98,12 @@
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -119,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -147,6 +159,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -591,9 +607,9 @@
           <t>The Tomorrow, Spot, Today options are already reflected on the deal date and Value date fields, so they should be removed from this dropdown.</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -631,9 +647,9 @@
           <t>Pertains to which PJL Group company will be transacting the deal (CLSC/PJ/Verite etc.) Should appear as a new tab alongside Companies, Banks, Transaction Types, Transfer Types, Currencies.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -671,9 +687,9 @@
           <t>The Source (From) 'Company' dropdown becomes 'Counterparty'.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -711,9 +727,9 @@
           <t>Example: 'Counterparty: Cebuana Lhuillier Services Corp' - a fixed, uneditable field reflecting the chosen counterparty.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -751,9 +767,9 @@
           <t>A new Transfer Type 'FX-Intercompany' was created via admin access. Both Source and Destination should show Counterparty instead of Company.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -791,9 +807,9 @@
           <t>The existing Ours box gets renamed based on transfer type.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -831,9 +847,9 @@
           <t>A second Ours section is needed for the buying counterparty in FX Inter-Company deals.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -871,9 +887,9 @@
           <t>One SALE line and one BUY line with the same reference number (suffixed .1 and .2). The only change between lines is the transaction_type column.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -911,9 +927,9 @@
           <t>A TMS-tailored report capturing only the fields required for SAP mass upload. Similar to Settlement Report but with specific column filtering.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>NOT IMPLEMENTED</t>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -951,9 +967,9 @@
           <t>The simplified layout shows: single currency dropdown, Currency Amount, Exchange Rate, and Converted Amount (no currency codes in labels). The previously requested divide function should be removed.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>CONFLICTS WITH PRIOR IMPLEMENTATION</t>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -981,7 +997,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -991,7 +1007,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1001,17 +1017,17 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Conflicts with Prior:</t>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Implemented:</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
